--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91724</v>
+        <v>91729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91729</v>
+        <v>91733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91733</v>
+        <v>91738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91758</v>
+        <v>91765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91765</v>
+        <v>91767</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91767</v>
+        <v>91776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>128822961</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128836015</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>128835978</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>128822958</v>
       </c>
       <c r="B6" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128822951</v>
       </c>
       <c r="B2" t="n">
-        <v>91777</v>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128822961</v>
+        <v>128822958</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506716</v>
+        <v>506393</v>
       </c>
       <c r="R3" t="n">
-        <v>6537485</v>
+        <v>6537433</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,11 +900,11 @@
         <v>128822959</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128836015</v>
+        <v>128822961</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,44 +1019,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506452</v>
+        <v>506716</v>
       </c>
       <c r="R5" t="n">
-        <v>6537463</v>
+        <v>6537485</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,76 +1096,78 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128822958</v>
+        <v>128835978</v>
       </c>
       <c r="B6" t="n">
-        <v>96302</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506393</v>
+        <v>506701</v>
       </c>
       <c r="R6" t="n">
-        <v>6537433</v>
+        <v>6537489</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,55 +1205,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835978</v>
+        <v>128836015</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506701</v>
+        <v>506452</v>
       </c>
       <c r="R7" t="n">
-        <v>6537489</v>
+        <v>6537463</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,7 +1332,7 @@
         <v>128836054</v>
       </c>
       <c r="B8" t="n">
-        <v>92860</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3669-2023 artfynd.xlsx
+++ b/artfynd/A 3669-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822951</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822958</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822959</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128836015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128836054</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822961</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,8 +1466,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>